--- a/dapan/cnttnc/Ket_Qua_Exel.xlsx
+++ b/dapan/cnttnc/Ket_Qua_Exel.xlsx
@@ -730,6 +730,21 @@
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
         <c:spPr>
           <a:solidFill>
             <a:schemeClr val="accent1"/>
@@ -2442,7 +2457,7 @@
     <col min="9" max="9" width="8.90625" style="1"/>
     <col min="10" max="10" width="10.90625" style="1" customWidth="1"/>
     <col min="11" max="11" width="10.26953125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7265625" style="1" customWidth="1"/>
     <col min="13" max="13" width="8.90625" style="1"/>
     <col min="14" max="14" width="12.08984375" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="9.54296875" style="1" bestFit="1" customWidth="1"/>
